--- a/개인적인/이혼증거/재산목록/월급과월세내역및생활비예상내가가져간금액계좌내역으로작성(공동재산과개인재산).xlsx
+++ b/개인적인/이혼증거/재산목록/월급과월세내역및생활비예상내가가져간금액계좌내역으로작성(공동재산과개인재산).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\pythonEduNoteTxt\개인적인\이혼증거\재산목록\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\pythonEduNoteTxt\개인적인\이혼증거\가사조사\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5632BD3C-656E-4816-9375-A0EDB13CF602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A13888-9DFD-4825-8A74-BFFF1C220F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="70">
   <si>
     <t>21년</t>
   </si>
@@ -231,10 +231,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>신명한국부동산오른금액</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>결혼식자금</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -247,27 +243,47 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>투입후남은금액</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>2020년9월3일</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>투입후남은금액일자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021년4월12일</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>월세보증금</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>2021년11월01일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026년02월10일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>피고 KB손보교통사고처리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025년04월14일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>변호사비용(이혼조정)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>토스뱅크</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000-1875-0867</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025년07월14일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>변호사비용(이혼소송)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2058,8 +2074,8 @@
         <v>17</v>
       </c>
       <c r="B63" s="3">
-        <f>C63+D63+F63+G63</f>
-        <v>266535715</v>
+        <f>C63+D63+F63</f>
+        <v>272435715</v>
       </c>
       <c r="C63" s="3">
         <f>SUM(C2:C62)</f>
@@ -2111,23 +2127,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75410B7-E882-40EB-8BF1-B9F60E61D93B}">
-  <dimension ref="B2:K19"/>
+  <dimension ref="B2:I22"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="21.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.69921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B2" s="7" t="s">
         <v>30</v>
       </c>
@@ -2135,31 +2150,25 @@
         <v>31</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="K2" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="7" t="s">
         <v>38</v>
       </c>
@@ -2167,28 +2176,22 @@
         <v>39</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I3">
+      <c r="H3">
         <v>31360016</v>
       </c>
-      <c r="J3">
-        <v>31360016</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B4" s="7" t="s">
         <v>43</v>
       </c>
@@ -2196,202 +2199,224 @@
         <v>44</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I4">
+      <c r="H4">
         <v>65000000</v>
       </c>
-      <c r="J4">
-        <v>65000000</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B5" s="7" t="s">
         <v>46</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="I5">
+      <c r="H5">
         <v>6461716</v>
       </c>
-      <c r="J5">
-        <v>6461716</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B6" s="7" t="s">
         <v>50</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="7"/>
+        <v>57</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="E6" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I6">
+      <c r="H6">
         <v>10000000</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="I6" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B7" s="7" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7">
+        <v>10365063</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8">
+        <v>3000000</v>
+      </c>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B9" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="C9" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7">
-        <v>10365063</v>
-      </c>
-      <c r="J7">
-        <v>4330000</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B8" s="7" t="s">
+      <c r="E9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9">
+        <v>4000000</v>
+      </c>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B10" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="D10" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10">
+        <v>4400000</v>
+      </c>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8">
-        <v>3000000</v>
-      </c>
-      <c r="J8">
-        <v>3000000</v>
-      </c>
-      <c r="K8" s="7"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B9" s="7" t="s">
+      <c r="E11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11">
+        <v>2200000</v>
+      </c>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="D12" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="I9">
-        <f>SUM(I3:I8)</f>
-        <v>126186795</v>
-      </c>
-      <c r="J9">
-        <f>SUM(J3:J8)</f>
-        <v>110151732</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B18" s="7" t="s">
+      <c r="H12">
+        <f>SUM(H3:H11)</f>
+        <v>136786795</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B21" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C21" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B19">
-        <v>0.7</v>
-      </c>
-      <c r="C19" t="str">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B22">
+        <v>0.6</v>
+      </c>
+      <c r="C22" t="str">
         <f>공동재산!A63</f>
         <v>합계</v>
       </c>
-      <c r="D19">
+      <c r="D22">
         <f>공동재산!B63</f>
-        <v>266535715</v>
-      </c>
-      <c r="E19">
-        <v>100000000</v>
-      </c>
-      <c r="F19">
-        <f>J9+(D19*B19)+(E19*0.5)</f>
-        <v>346726732.5</v>
+        <v>272435715</v>
+      </c>
+      <c r="E22">
+        <f>H12+(D22*B22)</f>
+        <v>300248224</v>
       </c>
     </row>
   </sheetData>
